--- a/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos</t>
+          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,88; 16,76</t>
+          <t>13,86; 16,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,22; 13,65</t>
+          <t>10,27; 13,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,12; 15,59</t>
+          <t>11,06; 15,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 12,6</t>
+          <t>8,44; 12,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 16,85</t>
+          <t>12,67; 17,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,53; 16,48</t>
+          <t>11,6; 16,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 11,32</t>
+          <t>9,19; 11,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 16,7</t>
+          <t>7,08; 16,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 16,11</t>
+          <t>13,6; 15,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 14,3</t>
+          <t>11,17; 14,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 12,91</t>
+          <t>10,43; 12,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 14,3</t>
+          <t>8,5; 14,15</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 14,48</t>
+          <t>13,15; 14,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,4; 12,91</t>
+          <t>11,34; 12,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 11,94</t>
+          <t>10,76; 11,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 17,77</t>
+          <t>11,56; 17,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,04; 14,26</t>
+          <t>13,02; 14,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 12,21</t>
+          <t>10,92; 12,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 12,86</t>
+          <t>11,34; 12,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,0; 14,12</t>
+          <t>11,09; 14,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 14,16</t>
+          <t>13,25; 14,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 12,33</t>
+          <t>11,32; 12,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 12,14</t>
+          <t>11,21; 12,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 15,04</t>
+          <t>11,88; 15,08</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,57; 15,54</t>
+          <t>13,58; 15,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,81</t>
+          <t>11,33; 13,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 12,87</t>
+          <t>11,0; 12,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 17,29</t>
+          <t>10,61; 17,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,61; 16,05</t>
+          <t>13,75; 16,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,36</t>
+          <t>11,38; 13,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,12</t>
+          <t>11,17; 13,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,86; 19,6</t>
+          <t>11,71; 19,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 15,36</t>
+          <t>13,83; 15,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,57; 13,28</t>
+          <t>11,63; 13,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,71</t>
+          <t>11,31; 12,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,73</t>
+          <t>11,91; 16,94</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 14,59</t>
+          <t>13,59; 14,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,65</t>
+          <t>11,47; 12,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,07</t>
+          <t>11,08; 12,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,8</t>
+          <t>11,82; 16,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 14,54</t>
+          <t>13,37; 14,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,54</t>
+          <t>11,37; 12,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 12,45</t>
+          <t>11,37; 12,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 14,38</t>
+          <t>11,45; 14,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,34</t>
+          <t>13,64; 14,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 12,34</t>
+          <t>11,6; 12,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 12,11</t>
+          <t>11,34; 12,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,08; 14,49</t>
+          <t>12,16; 14,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,86; 16,82</t>
+          <t>13,63; 16,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 13,68</t>
+          <t>10,28; 13,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 15,35</t>
+          <t>11,11; 15,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 12,74</t>
+          <t>8,26; 12,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,09</t>
+          <t>12,57; 16,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 16,61</t>
+          <t>11,48; 16,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 11,35</t>
+          <t>9,08; 11,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 16,42</t>
+          <t>7,39; 17,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 15,93</t>
+          <t>13,59; 15,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 14,14</t>
+          <t>11,2; 14,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,43; 12,75</t>
+          <t>10,43; 12,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 14,15</t>
+          <t>8,44; 14,25</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 14,38</t>
+          <t>13,11; 14,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,8</t>
+          <t>11,43; 12,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 11,99</t>
+          <t>10,74; 11,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 17,87</t>
+          <t>11,71; 18,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,02; 14,28</t>
+          <t>13,09; 14,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 12,18</t>
+          <t>10,99; 12,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,83</t>
+          <t>11,36; 12,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 14,33</t>
+          <t>10,96; 14,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,25; 14,14</t>
+          <t>13,22; 14,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 12,28</t>
+          <t>11,3; 12,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 12,18</t>
+          <t>11,21; 12,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 15,08</t>
+          <t>11,69; 15,07</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,58; 15,49</t>
+          <t>13,46; 15,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,58</t>
+          <t>11,39; 13,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 12,95</t>
+          <t>11,0; 12,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,39</t>
+          <t>11,0; 17,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 16,24</t>
+          <t>13,6; 16,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 13,44</t>
+          <t>11,43; 13,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,17; 13,24</t>
+          <t>11,08; 13,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,54</t>
+          <t>11,82; 19,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 15,37</t>
+          <t>13,89; 15,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,63; 13,16</t>
+          <t>11,55; 13,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 12,59</t>
+          <t>11,29; 12,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 16,94</t>
+          <t>12,07; 17,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 14,57</t>
+          <t>13,58; 14,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,63</t>
+          <t>11,47; 12,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,05</t>
+          <t>11,07; 12,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,51</t>
+          <t>12,02; 16,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 14,46</t>
+          <t>13,42; 14,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,46</t>
+          <t>11,44; 12,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,49</t>
+          <t>11,29; 12,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 14,27</t>
+          <t>11,61; 14,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 14,36</t>
+          <t>13,62; 14,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 12,37</t>
+          <t>11,59; 12,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,09</t>
+          <t>11,36; 12,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,16; 14,55</t>
+          <t>12,12; 14,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo que dura el trayecto desde su domicilio al médico en minutos (tasa de respuesta: 95,27%)</t>
+          <t>Tiempo medio en minutos que dura el trayecto desde su domicilio a la consulta médica (tasa de respuesta: 95,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11,26</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,31</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12,56</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,01</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,55</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,19</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,06</t>
+          <t>10,88</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,93</t>
+          <t>11,11</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,63; 16,74</t>
+          <t>12,64; 16,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,83</t>
+          <t>11,53; 16,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,5</t>
+          <t>9,19; 11,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,62</t>
+          <t>7,26; 17,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 16,52</t>
+          <t>13,88; 16,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 16,6</t>
+          <t>10,22; 13,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 11,27</t>
+          <t>11,12; 15,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 17,16</t>
+          <t>8,6; 12,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 15,99</t>
+          <t>13,58; 16,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,2; 14,0</t>
+          <t>11,27; 14,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,43; 12,9</t>
+          <t>10,48; 12,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,25</t>
+          <t>8,76; 14,74</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,52</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,02</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,63</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>13,69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,04</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,28</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,02</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,61</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,52</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,43</t>
+          <t>13,96</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,12</t>
+          <t>13,22</t>
         </is>
       </c>
     </row>
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 14,4</t>
+          <t>13,04; 14,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 12,85</t>
+          <t>10,95; 12,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 11,99</t>
+          <t>11,35; 12,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 18,54</t>
+          <t>11,21; 14,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,09; 14,39</t>
+          <t>13,11; 14,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 12,15</t>
+          <t>11,4; 12,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 12,94</t>
+          <t>10,75; 11,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 14,13</t>
+          <t>11,45; 17,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 12,24</t>
+          <t>11,32; 12,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 12,15</t>
+          <t>11,19; 12,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 15,07</t>
+          <t>11,82; 15,18</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,02</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14,42</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>14,37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,37</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,85</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,74</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,25</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,17</t>
+          <t>13,78</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,88</t>
+          <t>14,12</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 15,43</t>
+          <t>13,61; 16,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 13,9</t>
+          <t>11,33; 13,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 12,88</t>
+          <t>11,2; 13,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,79</t>
+          <t>11,98; 20,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 16,08</t>
+          <t>13,57; 15,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 13,46</t>
+          <t>11,33; 13,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 13,13</t>
+          <t>10,99; 12,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,82; 19,89</t>
+          <t>10,82; 18,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,89; 15,3</t>
+          <t>13,85; 15,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,55; 13,15</t>
+          <t>11,57; 13,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,74</t>
+          <t>11,29; 12,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 17,71</t>
+          <t>12,06; 17,19</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,91</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,85</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,97</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14,04</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12,02</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,53</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,91</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,91</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>13,72</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>13,31</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,57</t>
+          <t>13,46; 14,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,6</t>
+          <t>11,34; 12,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,07</t>
+          <t>11,33; 12,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,59</t>
+          <t>11,65; 14,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,42; 14,53</t>
+          <t>13,53; 14,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 12,51</t>
+          <t>11,47; 12,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,47</t>
+          <t>11,08; 12,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 14,21</t>
+          <t>11,96; 16,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 14,36</t>
+          <t>13,63; 14,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,39</t>
+          <t>11,6; 12,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 12,1</t>
+          <t>11,32; 12,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 14,64</t>
+          <t>12,14; 14,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18C_M-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>14,01</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,26</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,31</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,56</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10,88</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14,61</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12,36</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11,32</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,11</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>14.00626584106079</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>13.55041442783469</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10.1855673311221</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11.25719035318485</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>15.20100607231529</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>11.30512300343334</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>12.55634020942579</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>10.87902970165125</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>14.61336476951039</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>12.35622272109096</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>11.32120914096651</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>11.10753197978736</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,64; 16,85</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11,53; 16,48</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9,19; 11,32</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7,26; 17,31</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,88; 16,76</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,22; 13,65</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,12; 15,59</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,6; 12,74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13,58; 16,11</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11,27; 14,3</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10,48; 12,91</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,76; 14,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>12.64387770619251</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>11.53067292028057</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>9.186397146736669</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>7.257839064616136</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>13.87715613902956</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>10.22422382642459</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>11.11986089478229</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>8.597715736145835</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>13.57544612693171</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>11.27054267942446</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>10.47513840901537</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>8.763989496692625</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>16.85129104606708</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.48002267210222</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.31948337978287</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>17.30961106039781</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>16.75631997938095</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>13.64846764342254</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>15.59001524601097</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>12.73756938723317</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>16.11397012066875</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>14.29877132266299</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>12.90545704287247</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>14.73926165068067</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>13,61</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11,52</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,63</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,69</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,04</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13,96</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13,65</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11,77</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11,65</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13,04; 14,26</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,95; 12,21</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11,35; 12,86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11,21; 14,52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,11; 14,48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,4; 12,91</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,75; 11,94</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11,45; 17,74</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13,22; 14,16</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11,32; 12,33</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11,19; 12,14</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,82; 15,18</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>13.60660120989549</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>11.51624645583094</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>12.02163866700827</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>12.63398276953816</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>13.69133106387632</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>12.04256868599443</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>11.28029883259016</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>13.96106471360562</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>13.64726751220749</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>11.76734638225169</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>11.65248691304362</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>13.22258122759979</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>14,74</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,37</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,37</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13,78</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14,55</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12,31</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11,94</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>14,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>13.03806810515345</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>10.94591271884674</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>11.34632777169178</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>11.21131537174025</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>13.10865201803472</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>11.40010892671434</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>10.74777668147901</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>11.45345721631234</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>13.22062371868973</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>11.31747111544501</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>11.18602248055903</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>11.81556969743191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>13,61; 16,05</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 13,36</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>11,2; 13,12</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>11,98; 20,19</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>13,57; 15,54</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 13,81</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,99; 12,87</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10,82; 18,19</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13,85; 15,36</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>11,57; 13,28</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11,29; 12,71</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 17,19</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>14.26497813429941</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>12.21040134895681</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>12.85634398153995</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>14.52051904736397</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>14.48213983326769</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>12.90836202869856</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>11.94248969402151</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>17.73916960084877</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>14.16402819914252</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>12.32797701910108</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>12.13984027776518</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>15.17727988379702</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>13,91</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11,91</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,97</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,04</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,53</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13,72</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13,98</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11,96</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11,69</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,31</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>14.74444026003912</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>12.2490334595415</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>12.01780104076677</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>14.41947116585094</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>14.37210947251485</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.36779879651018</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>11.85071301169994</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>13.78447972671935</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>14.55342835153786</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>12.30654361890931</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>11.93998194309359</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>14.11632170876034</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>13,46; 14,54</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11,34; 12,54</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11,33; 12,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11,65; 14,71</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,53; 14,59</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,47; 12,65</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,08; 12,07</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11,96; 16,86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13,63; 14,34</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11,6; 12,34</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11,32; 12,11</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>12,14; 14,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>13.61179031310808</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>11.330763219006</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>11.19510999636799</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>11.97952752492134</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>13.57289586304012</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>11.3318762224193</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10.98768423471361</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>10.8245245462373</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>13.85132184975572</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>11.57193712470784</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>11.28648274849039</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>12.06337768065324</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>16.04901020445829</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.35754255490177</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.1168961859044</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.18711246616758</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>15.54269561497485</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>13.80722065610816</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>12.86885901306262</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>18.18547134651975</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>15.35545718130574</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>13.28224848003288</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>12.70764760273785</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>17.19454468538276</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>13.91343531556502</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>11.90567568435973</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>11.85040433136647</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>12.96750362173543</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>14.04437981032134</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>12.02288604179287</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>11.52944666064165</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>13.71931023165148</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>13.97775367206355</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>11.96254778412097</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>11.693703793222</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>13.30503018326292</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>13.45726946100685</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>11.33864648964353</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>11.33343395249603</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>11.6506891724136</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>13.53059226186534</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11.46951661894438</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>11.08401096954695</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>11.95575165745194</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>13.63367168082407</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>11.59855595350391</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>11.32382013119831</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>12.13938202892009</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>14.53706552506631</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>12.54263774431316</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>12.44983585425031</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>14.70568462762993</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>14.58879493748012</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>12.65209444523252</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>12.0732040857605</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>16.85542541423531</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>14.33858010270268</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>12.33696968373931</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>12.11308658897577</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>14.82787926282703</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
